--- a/CADASTRO DE CLIENTES.xlsx
+++ b/CADASTRO DE CLIENTES.xlsx
@@ -404,7 +404,7 @@
         <v>Relatório de clientes</v>
       </c>
       <c r="B1" t="str">
-        <v>Gerado em 31/08/2026 às 15:12:36</v>
+        <v>Gerado em 31/08/2026 às 19:18:23</v>
       </c>
     </row>
     <row r="2">
